--- a/data/trans_orig/Q5409-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5409-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2007</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4656</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4824</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,62 +881,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5543</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>5916</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28900</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67406</t>
+          <t>67582</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73811</t>
+          <t>73810</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6149</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1224</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6662</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6164</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6292</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>19139</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56100</t>
+          <t>56500</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64759</t>
+          <t>64729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82744</t>
+          <t>83549</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94389</t>
+          <t>94598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143190</t>
+          <t>143459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157289</t>
+          <t>157987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7794</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>2288</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7773</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>8141</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2288</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6914</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>948</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45877</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72074</t>
+          <t>73169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82368</t>
+          <t>82350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>122316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132418</t>
+          <t>132381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>11008</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49857</t>
+          <t>49655</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60533</t>
+          <t>60329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71056</t>
+          <t>71075</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112785</t>
+          <t>112896</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124566</t>
+          <t>125010</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -2557,82 +2557,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2287</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7023</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>17,03%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>2287</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6871</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2287</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28038</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52575</t>
+          <t>52644</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64725</t>
+          <t>64865</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -3013,97 +3013,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>6720</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5844</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>5676</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42494</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58965</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69105</t>
+          <t>69090</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105695</t>
+          <t>105208</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115349</t>
+          <t>115362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98644</t>
+          <t>98678</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105115</t>
+          <t>105125</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107610</t>
+          <t>107441</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116068</t>
+          <t>116083</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>210021</t>
+          <t>210149</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>220277</t>
+          <t>220220</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19372</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>27041</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>40678</t>
+          <t>40903</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>88711</t>
+          <t>88328</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>102866</t>
+          <t>102562</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>115642</t>
+          <t>115823</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>135425</t>
+          <t>135604</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>209719</t>
+          <t>209634</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>234732</t>
+          <t>234664</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>38891</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>38076</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>29399</t>
+          <t>29389</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>54812</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>52658</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>85466</t>
+          <t>84314</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>456411</t>
+          <t>458017</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>477807</t>
+          <t>478159</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>598254</t>
+          <t>599640</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>628518</t>
+          <t>629432</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1064700</t>
+          <t>1063421</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1101847</t>
+          <t>1100308</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2012</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35408</t>
+          <t>34776</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43273</t>
+          <t>43233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>26822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>39359</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64847</t>
+          <t>65101</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80477</t>
+          <t>80956</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22708</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27243</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>18757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29095</t>
+          <t>28597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61824</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75841</t>
+          <t>75897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66579</t>
+          <t>66989</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84817</t>
+          <t>85478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135049</t>
+          <t>135733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157960</t>
+          <t>157639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41762</t>
+          <t>40490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52681</t>
+          <t>52698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60797</t>
+          <t>61013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73573</t>
+          <t>73625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108143</t>
+          <t>107294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124382</t>
+          <t>124139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11608</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54125</t>
+          <t>53425</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62874</t>
+          <t>62857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69363</t>
+          <t>69823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81422</t>
+          <t>81371</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128699</t>
+          <t>128900</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142954</t>
+          <t>143083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,62 +6932,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5363</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5036</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>26054</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>20418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>29410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29916</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41833</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>54230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69892</t>
+          <t>69736</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17771</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>40047</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48607</t>
+          <t>49562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67076</t>
+          <t>67039</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>100692</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114454</t>
+          <t>114433</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20363</t>
+          <t>19967</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22675</t>
+          <t>21160</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34874</t>
+          <t>34636</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90866</t>
+          <t>91088</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107662</t>
+          <t>107101</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>116081</t>
+          <t>115899</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>132336</t>
+          <t>132078</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>213928</t>
+          <t>215617</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>236169</t>
+          <t>236432</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17698</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>31786</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>103600</t>
+          <t>104994</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>117589</t>
+          <t>117576</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>130146</t>
+          <t>131335</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>149150</t>
+          <t>149102</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>241119</t>
+          <t>242155</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>264672</t>
+          <t>264372</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>34897</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>63460</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>42747</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>72854</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>61605</t>
+          <t>59091</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>58669</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>91064</t>
+          <t>91840</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>99837</t>
+          <t>101166</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>142882</t>
+          <t>143888</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>486674</t>
+          <t>490906</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>519142</t>
+          <t>521194</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>598070</t>
+          <t>599098</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>641223</t>
+          <t>639617</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1098464</t>
+          <t>1098428</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1150934</t>
+          <t>1149976</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2016</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>13359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18704</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26936</t>
+          <t>27246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34836</t>
+          <t>34753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28243</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41665</t>
+          <t>42438</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57721</t>
+          <t>56415</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74634</t>
+          <t>73319</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -9869,97 +9869,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1838</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7966</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2430</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8456</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>8644</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2430</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>8221</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80190</t>
+          <t>80560</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86576</t>
+          <t>86563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103911</t>
+          <t>103657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113963</t>
+          <t>113914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187403</t>
+          <t>187446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198950</t>
+          <t>199318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13943</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>20143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54119</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62030</t>
+          <t>62009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60248</t>
+          <t>59921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74858</t>
+          <t>74869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119355</t>
+          <t>118270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134980</t>
+          <t>135169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21294</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22198</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54988</t>
+          <t>55944</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63008</t>
+          <t>63114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62094</t>
+          <t>61719</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79865</t>
+          <t>79753</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121288</t>
+          <t>121943</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140195</t>
+          <t>140587</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -11237,97 +11237,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1888</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>789</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43411</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85047</t>
+          <t>84684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91817</t>
+          <t>91823</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29449</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41067</t>
+          <t>41405</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62431</t>
+          <t>62576</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>83005</t>
+          <t>84575</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>100128</t>
+          <t>100998</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20655</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>26133</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48293</t>
+          <t>47718</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>36157</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>63948</t>
+          <t>62958</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89212</t>
+          <t>89681</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>104480</t>
+          <t>105255</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>94754</t>
+          <t>95834</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>117767</t>
+          <t>118412</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>189785</t>
+          <t>191302</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>219767</t>
+          <t>219213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>14060</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>124671</t>
+          <t>125391</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>132514</t>
+          <t>132512</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>155054</t>
+          <t>156324</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>171229</t>
+          <t>170640</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,47 +12881,47 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>295262</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>284755</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>301560</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>91,72%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
           <t>97,13%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>295262</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>285149</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>300913</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>30099</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>58467</t>
+          <t>59582</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>53729</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>61041</t>
+          <t>59897</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>97567</t>
+          <t>98575</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>97696</t>
+          <t>99251</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>141697</t>
+          <t>142218</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>527256</t>
+          <t>527169</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>553524</t>
+          <t>553188</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>645385</t>
+          <t>642517</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>685599</t>
+          <t>687376</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1180532</t>
+          <t>1180332</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1228905</t>
+          <t>1231650</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2023</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,97 +13753,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54626</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56267</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61900</t>
+          <t>61920</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>111910</t>
+          <t>112463</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118026</t>
+          <t>118074</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72983</t>
+          <t>74021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79894</t>
+          <t>79898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103582</t>
+          <t>104081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115557</t>
+          <t>115915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179539</t>
+          <t>180531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194435</t>
+          <t>194655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>25234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58689</t>
+          <t>58701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67820</t>
+          <t>67640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65680</t>
+          <t>64687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76128</t>
+          <t>75525</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127359</t>
+          <t>127603</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140863</t>
+          <t>141191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61590</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69824</t>
+          <t>69786</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>81061</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90295</t>
+          <t>90451</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>145155</t>
+          <t>145497</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158388</t>
+          <t>157814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>25956</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32340</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42266</t>
+          <t>42388</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>49824</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71793</t>
+          <t>71084</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80858</t>
+          <t>80873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45896</t>
+          <t>45865</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53379</t>
+          <t>53647</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54203</t>
+          <t>54081</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60354</t>
+          <t>60288</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102803</t>
+          <t>101531</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112482</t>
+          <t>111859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>65831</t>
+          <t>64998</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>83346</t>
+          <t>83329</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>94235</t>
+          <t>94062</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109098</t>
+          <t>108800</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>252802</t>
+          <t>252051</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>330047</t>
+          <t>332080</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>361432</t>
+          <t>361318</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>444895</t>
+          <t>445647</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17533</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>21659</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>26299</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>20287</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34387</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>129029</t>
+          <t>129250</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>139119</t>
+          <t>139152</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>147725</t>
+          <t>147296</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>163072</t>
+          <t>163045</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>281778</t>
+          <t>282085</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>300154</t>
+          <t>300432</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>53216</t>
+          <t>52756</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>36058</t>
+          <t>31962</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>68446</t>
+          <t>68146</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41095</t>
+          <t>42090</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>63173</t>
+          <t>65131</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>53158</t>
+          <t>56811</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>128915</t>
+          <t>126074</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>96123</t>
+          <t>101367</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>177023</t>
+          <t>177883</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>568147</t>
+          <t>566892</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>591915</t>
+          <t>592757</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>854242</t>
+          <t>857552</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>955936</t>
+          <t>954106</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1442072</t>
+          <t>1440919</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1546959</t>
+          <t>1547649</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5409-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5409-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34582</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67582</t>
+          <t>66881</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73810</t>
+          <t>73808</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56500</t>
+          <t>56451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64729</t>
+          <t>65613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83549</t>
+          <t>83538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94598</t>
+          <t>94694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143459</t>
+          <t>144425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157987</t>
+          <t>157097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73169</t>
+          <t>72433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>82352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122316</t>
+          <t>123044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132381</t>
+          <t>132321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49655</t>
+          <t>49427</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60329</t>
+          <t>60450</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71075</t>
+          <t>71189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112896</t>
+          <t>113093</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>125010</t>
+          <t>125180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15969</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,49 +2798,49 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>34353</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>28375</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>38903</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>83,29%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>68,79%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>94,32%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>34353</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>28476</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>38863</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>83,29%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>69,04%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>94,22%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>62</t>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52644</t>
+          <t>52331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64865</t>
+          <t>64540</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>41692</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>59472</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69090</t>
+          <t>69092</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105208</t>
+          <t>105050</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115362</t>
+          <t>115240</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>822</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98678</t>
+          <t>98539</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>105130</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107441</t>
+          <t>107421</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116083</t>
+          <t>115981</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>210149</t>
+          <t>210072</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>220220</t>
+          <t>220267</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22074</t>
+          <t>21169</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>27041</t>
+          <t>26114</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>40903</t>
+          <t>41418</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>88328</t>
+          <t>88629</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>102562</t>
+          <t>102847</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>115823</t>
+          <t>115499</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>135604</t>
+          <t>135242</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>209634</t>
+          <t>209467</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>234664</t>
+          <t>233623</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38076</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>54812</t>
+          <t>54270</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52213</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>84314</t>
+          <t>84147</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>458017</t>
+          <t>456812</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>478159</t>
+          <t>478663</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>599640</t>
+          <t>597355</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>629432</t>
+          <t>629313</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1063421</t>
+          <t>1064970</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1100308</t>
+          <t>1102781</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14553</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>19414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34776</t>
+          <t>35008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43233</t>
+          <t>43298</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>38648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65101</t>
+          <t>64231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80956</t>
+          <t>80359</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23312</t>
+          <t>24117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15598</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18757</t>
+          <t>18903</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28597</t>
+          <t>27057</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61045</t>
+          <t>61020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75897</t>
+          <t>75950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66989</t>
+          <t>67467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85478</t>
+          <t>85234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135733</t>
+          <t>135230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157639</t>
+          <t>157449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>17677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40490</t>
+          <t>41236</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52698</t>
+          <t>52716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73625</t>
+          <t>73519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107294</t>
+          <t>105706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124139</t>
+          <t>124237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53425</t>
+          <t>53414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62857</t>
+          <t>62895</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69823</t>
+          <t>70116</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81371</t>
+          <t>81384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128900</t>
+          <t>128425</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143083</t>
+          <t>142848</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26054</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29410</t>
+          <t>29456</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29803</t>
+          <t>30134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41917</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54230</t>
+          <t>53515</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69736</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40047</t>
+          <t>40067</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49562</t>
+          <t>48657</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56481</t>
+          <t>55402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67039</t>
+          <t>67001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>99685</t>
+          <t>100019</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114433</t>
+          <t>114561</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19967</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21160</t>
+          <t>22884</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34636</t>
+          <t>34987</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>91088</t>
+          <t>91405</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107101</t>
+          <t>107239</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115899</t>
+          <t>115571</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>132078</t>
+          <t>132452</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>215617</t>
+          <t>213781</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>236432</t>
+          <t>236044</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17632</t>
+          <t>18683</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14231</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>32061</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>104994</t>
+          <t>103671</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>117576</t>
+          <t>117679</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>131335</t>
+          <t>131104</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>149102</t>
+          <t>149157</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>242155</t>
+          <t>240721</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>264372</t>
+          <t>263662</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>63460</t>
+          <t>61464</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>43309</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>72854</t>
+          <t>72059</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>59091</t>
+          <t>61720</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>58298</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>91840</t>
+          <t>92652</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>101166</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>143888</t>
+          <t>142613</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>490906</t>
+          <t>488107</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>521194</t>
+          <t>518090</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>599098</t>
+          <t>599549</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>639617</t>
+          <t>642552</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1098428</t>
+          <t>1102440</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1149976</t>
+          <t>1153699</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27246</t>
+          <t>26854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34753</t>
+          <t>34669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42438</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56415</t>
+          <t>57335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73319</t>
+          <t>73827</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80560</t>
+          <t>80198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>86566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103657</t>
+          <t>103551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113914</t>
+          <t>113908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187446</t>
+          <t>187570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199318</t>
+          <t>199419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12959</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53818</t>
+          <t>53957</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62009</t>
+          <t>61978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>60341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74869</t>
+          <t>74753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118270</t>
+          <t>117720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135169</t>
+          <t>134051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55944</t>
+          <t>54833</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63114</t>
+          <t>63032</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61719</t>
+          <t>62407</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79753</t>
+          <t>79647</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121943</t>
+          <t>121242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140587</t>
+          <t>140935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>807</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44091</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84684</t>
+          <t>84998</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91823</t>
+          <t>91805</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29436</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41405</t>
+          <t>41730</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>49548</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62576</t>
+          <t>62043</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>84575</t>
+          <t>83658</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>100998</t>
+          <t>100915</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47718</t>
+          <t>48146</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36157</t>
+          <t>36237</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62958</t>
+          <t>62280</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>90225</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105255</t>
+          <t>104918</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>95834</t>
+          <t>94431</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>118412</t>
+          <t>118285</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>191302</t>
+          <t>191684</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>219213</t>
+          <t>218722</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>869</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>125391</t>
+          <t>124462</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>132512</t>
+          <t>132480</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>156324</t>
+          <t>156106</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>170640</t>
+          <t>171171</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>284755</t>
+          <t>286124</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>301560</t>
+          <t>301512</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49140</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>58879</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>30306</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>53955</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>59897</t>
+          <t>60643</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>98575</t>
+          <t>98122</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>99251</t>
+          <t>99459</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>142218</t>
+          <t>140034</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>527169</t>
+          <t>527034</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>553188</t>
+          <t>553530</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>642517</t>
+          <t>643084</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>687376</t>
+          <t>687257</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1180332</t>
+          <t>1182439</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1231650</t>
+          <t>1230158</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -13896,32 +13896,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13931,32 +13931,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -14009,32 +14009,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60074</t>
+          <t>62141</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>58595</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61920</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14044,32 +14044,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115975</t>
+          <t>123096</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112463</t>
+          <t>119630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118074</t>
+          <t>125072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14239,32 +14239,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14274,22 +14274,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -14317,32 +14317,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14352,32 +14352,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -14430,32 +14430,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77994</t>
+          <t>85536</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74021</t>
+          <t>80804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>87466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14465,32 +14465,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>110430</t>
+          <t>115641</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104081</t>
+          <t>108179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115915</t>
+          <t>121566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14500,32 +14500,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>188424</t>
+          <t>201177</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180531</t>
+          <t>192708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194655</t>
+          <t>207651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128398</t>
+          <t>134719</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128398</t>
+          <t>134719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128398</t>
+          <t>134719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>209107</t>
+          <t>223092</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209107</t>
+          <t>223092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209107</t>
+          <t>223092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14660,32 +14660,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14730,32 +14730,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12371</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -14773,32 +14773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14808,32 +14808,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14843,32 +14843,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25234</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -14886,32 +14886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>63639</t>
+          <t>62502</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58701</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67640</t>
+          <t>66047</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14921,32 +14921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>69193</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64687</t>
+          <t>63572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75525</t>
+          <t>73958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14956,32 +14956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>134663</t>
+          <t>131695</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127603</t>
+          <t>124044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141191</t>
+          <t>137499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -14999,17 +14999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>616</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15186,32 +15186,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -15229,32 +15229,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15264,32 +15264,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15299,32 +15299,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>27200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -15342,32 +15342,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>66342</t>
+          <t>74731</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61482</t>
+          <t>69838</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69786</t>
+          <t>78559</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15377,32 +15377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>85906</t>
+          <t>91501</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81061</t>
+          <t>86227</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90451</t>
+          <t>96348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>152247</t>
+          <t>166233</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>145497</t>
+          <t>159280</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>157814</t>
+          <t>172486</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15490,17 +15490,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -15582,12 +15582,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>731</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15642,17 +15642,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -15685,32 +15685,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15755,32 +15755,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -15798,32 +15798,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25956</t>
+          <t>28267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>33959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15833,32 +15833,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46612</t>
+          <t>48346</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>44011</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49824</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15868,32 +15868,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>76499</t>
+          <t>79751</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71084</t>
+          <t>74737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80873</t>
+          <t>84811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -15911,17 +15911,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15981,17 +15981,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16028,67 +16028,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>5743</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3261</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>9095</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>8,53%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>5162</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2927</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>8084</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16098,32 +16098,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -16141,32 +16141,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16176,32 +16176,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16211,32 +16211,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -16254,32 +16254,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>50064</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45865</t>
+          <t>45827</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53647</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>58781</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54081</t>
+          <t>54838</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60288</t>
+          <t>61726</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16324,32 +16324,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>107451</t>
+          <t>108845</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>101531</t>
+          <t>104085</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111859</t>
+          <t>113428</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -16367,17 +16367,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16484,32 +16484,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16519,32 +16519,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23033</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16554,32 +16554,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -16597,32 +16597,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>23077</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26933</t>
+          <t>32811</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16632,32 +16632,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>64998</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16667,32 +16667,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>50813</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>40742</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>83329</t>
+          <t>63755</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -16710,27 +16710,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>101924</t>
+          <t>125595</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>115661</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108800</t>
+          <t>133587</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -16745,32 +16745,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>307752</t>
+          <t>127790</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>252051</t>
+          <t>118644</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>332080</t>
+          <t>135989</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,32 +16780,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>409677</t>
+          <t>253386</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>361318</t>
+          <t>239615</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>445647</t>
+          <t>264309</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -16823,17 +16823,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16858,17 +16858,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16940,32 +16940,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16975,32 +16975,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16487</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17010,32 +17010,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>11328</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -17053,32 +17053,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17088,32 +17088,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>15760</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17123,32 +17123,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>26667</t>
+          <t>31304</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>35422</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -17166,32 +17166,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>134900</t>
+          <t>149374</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>129250</t>
+          <t>142674</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>139152</t>
+          <t>154549</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17201,32 +17201,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>156508</t>
+          <t>177259</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>147296</t>
+          <t>167390</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>163045</t>
+          <t>185343</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17236,32 +17236,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>291408</t>
+          <t>326633</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>282085</t>
+          <t>314466</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>300432</t>
+          <t>336512</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -17279,17 +17279,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>146475</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>146475</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>146475</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>186092</t>
+          <t>212151</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186092</t>
+          <t>212151</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186092</t>
+          <t>212151</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17349,17 +17349,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>332567</t>
+          <t>375053</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>332567</t>
+          <t>375053</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>332567</t>
+          <t>375053</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17396,32 +17396,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17431,32 +17431,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>39019</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>52756</t>
+          <t>56985</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17466,32 +17466,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>55884</t>
+          <t>61729</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>31962</t>
+          <t>51408</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>74839</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -17509,32 +17509,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>52120</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>42090</t>
+          <t>46594</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>65131</t>
+          <t>70881</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17544,32 +17544,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>97871</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>56811</t>
+          <t>93849</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>122872</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17579,32 +17579,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>149991</t>
+          <t>165313</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>101367</t>
+          <t>145980</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>177883</t>
+          <t>186255</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -17622,32 +17622,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>580587</t>
+          <t>640162</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>566892</t>
+          <t>625117</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>592757</t>
+          <t>652826</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17657,32 +17657,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>895756</t>
+          <t>750654</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>857552</t>
+          <t>730699</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>954106</t>
+          <t>766056</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17692,32 +17692,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1476344</t>
+          <t>1390816</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1440919</t>
+          <t>1367443</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1547649</t>
+          <t>1411539</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17770,17 +17770,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1032646</t>
+          <t>902120</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1032646</t>
+          <t>902120</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1032646</t>
+          <t>902120</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17805,17 +17805,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1682219</t>
+          <t>1617858</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1682219</t>
+          <t>1617858</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1682219</t>
+          <t>1617858</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
